--- a/data/trans_orig/P41C1_AOS_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada</t>
+          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada (tasa de respuesta: 93,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,45</t>
+          <t>2,28; 6,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,66</t>
+          <t>2,97; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,62</t>
+          <t>2,94; 5,86</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,99</t>
+          <t>1,16; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,89</t>
+          <t>1,69; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,14</t>
+          <t>1,62; 3,19</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,6</t>
+          <t>1,93; 4,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,04</t>
+          <t>2,6; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,31</t>
+          <t>2,47; 4,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C1_AOS_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Estudios-trans_orig.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,08</t>
+          <t>2,43; 6,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,59</t>
+          <t>2,63; 7,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,86</t>
+          <t>2,97; 5,76</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,17</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,06</t>
+          <t>1,17; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,07</t>
+          <t>1,73; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,19</t>
+          <t>1,55; 3,02</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,76</t>
+          <t>2,03; 4,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,07</t>
+          <t>2,41; 4,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,29</t>
+          <t>2,5; 4,3</t>
         </is>
       </c>
     </row>
